--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_CB NAVÀS VISCOLA.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_CB NAVÀS VISCOLA.xlsx
@@ -565,13 +565,13 @@
         <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>85.4134</v>
+        <v>46.5025</v>
       </c>
       <c r="E2" t="n">
-        <v>66.1208</v>
+        <v>37.1998</v>
       </c>
       <c r="F2" t="n">
-        <v>19.2929</v>
+        <v>9.3025</v>
       </c>
       <c r="G2" t="n">
         <v>37.1334</v>
@@ -610,13 +610,13 @@
         <v>46.2964</v>
       </c>
       <c r="S2" t="n">
-        <v>67.2015</v>
+        <v>28.2909</v>
       </c>
       <c r="T2" t="n">
-        <v>47.4486</v>
+        <v>18.5276</v>
       </c>
       <c r="U2" t="n">
-        <v>19.7529</v>
+        <v>9.763299999999999</v>
       </c>
       <c r="V2" t="n">
         <v>-23.2193</v>
@@ -643,13 +643,13 @@
         <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>65.6741</v>
+        <v>44.2398</v>
       </c>
       <c r="E3" t="n">
-        <v>41.4466</v>
+        <v>24.6189</v>
       </c>
       <c r="F3" t="n">
-        <v>24.2278</v>
+        <v>19.621</v>
       </c>
       <c r="G3" t="n">
         <v>33.9875</v>
@@ -688,13 +688,13 @@
         <v>56.4542</v>
       </c>
       <c r="S3" t="n">
-        <v>44.1698</v>
+        <v>22.7352</v>
       </c>
       <c r="T3" t="n">
-        <v>31.4448</v>
+        <v>14.617</v>
       </c>
       <c r="U3" t="n">
-        <v>12.7249</v>
+        <v>8.118399999999999</v>
       </c>
       <c r="V3" t="n">
         <v>-16.976</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. ZHURAVLOV</t>
+          <t>M. BATALLER LOPEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D4" t="n">
-        <v>28.3441</v>
+        <v>42.1308</v>
       </c>
       <c r="E4" t="n">
-        <v>15.379</v>
+        <v>29.0675</v>
       </c>
       <c r="F4" t="n">
-        <v>12.9649</v>
+        <v>13.0633</v>
       </c>
       <c r="G4" t="n">
-        <v>3.0915</v>
+        <v>22.0143</v>
       </c>
       <c r="H4" t="n">
-        <v>5.075200000000001</v>
+        <v>16.9799</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.983800000000001</v>
+        <v>5.034800000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>15.187</v>
+        <v>39.9841</v>
       </c>
       <c r="K4" t="n">
-        <v>12.8389</v>
+        <v>25.0882</v>
       </c>
       <c r="L4" t="n">
-        <v>2.348100000000001</v>
+        <v>14.8965</v>
       </c>
       <c r="M4" t="n">
-        <v>-12.0953</v>
+        <v>-17.9699</v>
       </c>
       <c r="N4" t="n">
-        <v>-7.764</v>
+        <v>-8.1081</v>
       </c>
       <c r="O4" t="n">
-        <v>-4.3316</v>
+        <v>-9.8614</v>
       </c>
       <c r="P4" t="n">
-        <v>7.4232</v>
+        <v>-5.6651</v>
       </c>
       <c r="Q4" t="n">
-        <v>-31.2547</v>
+        <v>-43.7566</v>
       </c>
       <c r="R4" t="n">
-        <v>38.6777</v>
+        <v>38.0917</v>
       </c>
       <c r="S4" t="n">
-        <v>17.4159</v>
+        <v>2.324</v>
       </c>
       <c r="T4" t="n">
-        <v>14.484</v>
+        <v>1.8139</v>
       </c>
       <c r="U4" t="n">
-        <v>2.9318</v>
+        <v>0.5102</v>
       </c>
       <c r="V4" t="n">
-        <v>0.4136000000000006</v>
+        <v>23.4572</v>
       </c>
       <c r="W4" t="n">
-        <v>16.9629</v>
+        <v>31.0261</v>
       </c>
       <c r="X4" t="n">
-        <v>-16.5495</v>
+        <v>-7.5686</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. BATALLER LOPEZ</t>
+          <t>A. MONTAGUT PUNTI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D5" t="n">
-        <v>24.1547</v>
+        <v>37.8784</v>
       </c>
       <c r="E5" t="n">
-        <v>17.8852</v>
+        <v>16.1195</v>
       </c>
       <c r="F5" t="n">
-        <v>6.2694</v>
+        <v>21.7595</v>
       </c>
       <c r="G5" t="n">
-        <v>22.0143</v>
+        <v>34.8425</v>
       </c>
       <c r="H5" t="n">
-        <v>16.9799</v>
+        <v>34.5462</v>
       </c>
       <c r="I5" t="n">
-        <v>5.034800000000001</v>
+        <v>0.2965999999999984</v>
       </c>
       <c r="J5" t="n">
-        <v>39.9841</v>
+        <v>56.4365</v>
       </c>
       <c r="K5" t="n">
-        <v>25.0882</v>
+        <v>43.4383</v>
       </c>
       <c r="L5" t="n">
-        <v>14.8965</v>
+        <v>12.9984</v>
       </c>
       <c r="M5" t="n">
-        <v>-17.9699</v>
+        <v>-21.5938</v>
       </c>
       <c r="N5" t="n">
-        <v>-8.1081</v>
+        <v>-8.892199999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>-9.8614</v>
+        <v>-12.7019</v>
       </c>
       <c r="P5" t="n">
-        <v>-5.6651</v>
+        <v>-2.5395</v>
       </c>
       <c r="Q5" t="n">
-        <v>-43.7566</v>
+        <v>-58.0165</v>
       </c>
       <c r="R5" t="n">
-        <v>38.0917</v>
+        <v>55.4774</v>
       </c>
       <c r="S5" t="n">
-        <v>-15.6523</v>
+        <v>1.2049</v>
       </c>
       <c r="T5" t="n">
-        <v>-9.368400000000001</v>
+        <v>1.187</v>
       </c>
       <c r="U5" t="n">
-        <v>-6.2838</v>
+        <v>0.01779999999999993</v>
       </c>
       <c r="V5" t="n">
-        <v>23.4572</v>
+        <v>4.370699999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>31.0261</v>
+        <v>16.5123</v>
       </c>
       <c r="X5" t="n">
-        <v>-7.5686</v>
+        <v>-12.1414</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. MONTAGUT PUNTI</t>
+          <t>P. MONÉS RIERA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>26</v>
       </c>
       <c r="D6" t="n">
-        <v>14.7258</v>
+        <v>29.3441</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4278999999999984</v>
+        <v>29.8979</v>
       </c>
       <c r="F6" t="n">
-        <v>14.2982</v>
+        <v>-0.5536999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>34.8425</v>
+        <v>12.6995</v>
       </c>
       <c r="H6" t="n">
-        <v>34.5462</v>
+        <v>3.7569</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2965999999999984</v>
+        <v>8.942899999999998</v>
       </c>
       <c r="J6" t="n">
-        <v>56.4365</v>
+        <v>45.6274</v>
       </c>
       <c r="K6" t="n">
-        <v>43.4383</v>
+        <v>19.6691</v>
       </c>
       <c r="L6" t="n">
-        <v>12.9984</v>
+        <v>25.9584</v>
       </c>
       <c r="M6" t="n">
-        <v>-21.5938</v>
+        <v>-32.928</v>
       </c>
       <c r="N6" t="n">
-        <v>-8.892199999999999</v>
+        <v>-15.9124</v>
       </c>
       <c r="O6" t="n">
-        <v>-12.7019</v>
+        <v>-17.0158</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.5395</v>
+        <v>8.7903</v>
       </c>
       <c r="Q6" t="n">
-        <v>-58.0165</v>
+        <v>-42.5845</v>
       </c>
       <c r="R6" t="n">
-        <v>55.4774</v>
+        <v>51.3752</v>
       </c>
       <c r="S6" t="n">
-        <v>-21.9476</v>
+        <v>5.9516</v>
       </c>
       <c r="T6" t="n">
-        <v>-14.5042</v>
+        <v>3.8079</v>
       </c>
       <c r="U6" t="n">
-        <v>-7.4434</v>
+        <v>2.1438</v>
       </c>
       <c r="V6" t="n">
-        <v>4.370699999999999</v>
+        <v>1.903</v>
       </c>
       <c r="W6" t="n">
-        <v>16.5123</v>
+        <v>23.0469</v>
       </c>
       <c r="X6" t="n">
-        <v>-12.1414</v>
+        <v>-21.1442</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. MONÉS RIERA</t>
+          <t>D. ZHURAVLOV</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,70 +952,70 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D7" t="n">
-        <v>13.79</v>
+        <v>20.1949</v>
       </c>
       <c r="E7" t="n">
-        <v>20.4756</v>
+        <v>6.8431</v>
       </c>
       <c r="F7" t="n">
-        <v>-6.6858</v>
+        <v>13.3515</v>
       </c>
       <c r="G7" t="n">
-        <v>12.6995</v>
+        <v>3.0915</v>
       </c>
       <c r="H7" t="n">
-        <v>3.7569</v>
+        <v>5.075200000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>8.942899999999998</v>
+        <v>-1.983800000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>45.6274</v>
+        <v>15.187</v>
       </c>
       <c r="K7" t="n">
-        <v>19.6691</v>
+        <v>12.8389</v>
       </c>
       <c r="L7" t="n">
-        <v>25.9584</v>
+        <v>2.348100000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>-32.928</v>
+        <v>-12.0953</v>
       </c>
       <c r="N7" t="n">
-        <v>-15.9124</v>
+        <v>-7.764</v>
       </c>
       <c r="O7" t="n">
-        <v>-17.0158</v>
+        <v>-4.3316</v>
       </c>
       <c r="P7" t="n">
-        <v>8.7903</v>
+        <v>7.4232</v>
       </c>
       <c r="Q7" t="n">
-        <v>-42.5845</v>
+        <v>-31.2547</v>
       </c>
       <c r="R7" t="n">
-        <v>51.3752</v>
+        <v>38.6777</v>
       </c>
       <c r="S7" t="n">
-        <v>-9.6029</v>
+        <v>9.266999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>-5.6142</v>
+        <v>5.9481</v>
       </c>
       <c r="U7" t="n">
-        <v>-3.9884</v>
+        <v>3.3184</v>
       </c>
       <c r="V7" t="n">
-        <v>1.903</v>
+        <v>0.4136000000000006</v>
       </c>
       <c r="W7" t="n">
-        <v>23.0469</v>
+        <v>16.9629</v>
       </c>
       <c r="X7" t="n">
-        <v>-21.1442</v>
+        <v>-16.5495</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>13</v>
       </c>
       <c r="D8" t="n">
-        <v>3.746700000000001</v>
+        <v>12.2335</v>
       </c>
       <c r="E8" t="n">
-        <v>-5.0311</v>
+        <v>0.7718000000000003</v>
       </c>
       <c r="F8" t="n">
-        <v>8.777900000000001</v>
+        <v>11.462</v>
       </c>
       <c r="G8" t="n">
         <v>2.5421</v>
@@ -1078,13 +1078,13 @@
         <v>18.3622</v>
       </c>
       <c r="S8" t="n">
-        <v>-8.115499999999999</v>
+        <v>0.3712</v>
       </c>
       <c r="T8" t="n">
-        <v>-5.0722</v>
+        <v>0.7305999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>-3.0432</v>
+        <v>-0.359</v>
       </c>
       <c r="V8" t="n">
         <v>3.6554</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>B. RODRÍGUEZ CHAVARRIA</t>
+          <t>D. YUSTE MALO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D9" t="n">
-        <v>2.5528</v>
+        <v>7.506400000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>2.2531</v>
+        <v>-0.7303999999999986</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2996</v>
+        <v>8.236799999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>3.0012</v>
+        <v>7.737499999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>1.2205</v>
+        <v>-3.4191</v>
       </c>
       <c r="I9" t="n">
-        <v>1.7807</v>
+        <v>11.1567</v>
       </c>
       <c r="J9" t="n">
-        <v>1.6727</v>
+        <v>14.476</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4309999999999999</v>
+        <v>-0.7331000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>1.2416</v>
+        <v>15.2092</v>
       </c>
       <c r="M9" t="n">
-        <v>1.3286</v>
+        <v>-6.7385</v>
       </c>
       <c r="N9" t="n">
-        <v>0.7895</v>
+        <v>-2.686</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5391</v>
+        <v>-4.0524</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-6.6417</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9767</v>
+        <v>-24.2225</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9766999999999999</v>
+        <v>17.5808</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4485</v>
+        <v>1.0276</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3385</v>
+        <v>-0.0139999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7869999999999999</v>
+        <v>1.0417</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>5.3826</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2186</v>
+        <v>9.0299</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2186</v>
+        <v>-3.6474</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L. FONT TÀPIA</t>
+          <t>B. RODRÍGUEZ CHAVARRIA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>1.729</v>
+        <v>2.9517</v>
       </c>
       <c r="E10" t="n">
-        <v>1.2749</v>
+        <v>2.5159</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4541</v>
+        <v>0.4358</v>
       </c>
       <c r="G10" t="n">
-        <v>1.6794</v>
+        <v>3.0012</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4249</v>
+        <v>1.2205</v>
       </c>
       <c r="I10" t="n">
-        <v>1.2544</v>
+        <v>1.7807</v>
       </c>
       <c r="J10" t="n">
-        <v>1.2749</v>
+        <v>1.6727</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0205</v>
+        <v>0.4309999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>1.2544</v>
+        <v>1.2416</v>
       </c>
       <c r="M10" t="n">
-        <v>0.4045</v>
+        <v>1.3286</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4045</v>
+        <v>0.7895</v>
       </c>
       <c r="O10" t="n">
+        <v>0.5391</v>
+      </c>
+      <c r="P10" t="n">
         <v>0</v>
       </c>
-      <c r="P10" t="n">
-        <v>0.1953</v>
-      </c>
       <c r="Q10" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.9766999999999999</v>
+      </c>
+      <c r="S10" t="n">
+        <v>-0.0495</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.6012999999999999</v>
+      </c>
+      <c r="U10" t="n">
+        <v>-0.6508</v>
+      </c>
+      <c r="V10" t="n">
         <v>0</v>
       </c>
-      <c r="R10" t="n">
-        <v>0.1953</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0.1315</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0.1315</v>
-      </c>
-      <c r="V10" t="n">
-        <v>-0.2772</v>
-      </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2772</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. YUSTE MALO</t>
+          <t>L. FONT TÀPIA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4824000000000002</v>
+        <v>1.6745</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.372100000000001</v>
+        <v>1.2749</v>
       </c>
       <c r="F11" t="n">
-        <v>6.8545</v>
+        <v>0.3996</v>
       </c>
       <c r="G11" t="n">
-        <v>7.737499999999999</v>
+        <v>1.6794</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.4191</v>
+        <v>0.4249</v>
       </c>
       <c r="I11" t="n">
-        <v>11.1567</v>
+        <v>1.2544</v>
       </c>
       <c r="J11" t="n">
-        <v>14.476</v>
+        <v>1.2749</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.7331000000000001</v>
+        <v>0.0205</v>
       </c>
       <c r="L11" t="n">
-        <v>15.2092</v>
+        <v>1.2544</v>
       </c>
       <c r="M11" t="n">
-        <v>-6.7385</v>
+        <v>0.4045</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.686</v>
+        <v>0.4045</v>
       </c>
       <c r="O11" t="n">
-        <v>-4.0524</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>-6.6417</v>
+        <v>0.1953</v>
       </c>
       <c r="Q11" t="n">
-        <v>-24.2225</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>17.5808</v>
+        <v>0.1953</v>
       </c>
       <c r="S11" t="n">
-        <v>-5.9962</v>
+        <v>0.077</v>
       </c>
       <c r="T11" t="n">
-        <v>-5.6557</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3406</v>
+        <v>0.077</v>
       </c>
       <c r="V11" t="n">
-        <v>5.3826</v>
+        <v>-0.2772</v>
       </c>
       <c r="W11" t="n">
-        <v>9.0299</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.6474</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>N. ARRANZ JARAMILLO</t>
+          <t>I. JUNCADELLA ENFEDAQUE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3647</v>
+        <v>1.1352</v>
       </c>
       <c r="E12" t="n">
-        <v>0.192</v>
+        <v>-10.304</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1728</v>
+        <v>11.4393</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3316</v>
+        <v>-3.5382</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8307</v>
+        <v>-2.517799999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.499</v>
+        <v>-1.0204</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6762</v>
+        <v>10.5942</v>
       </c>
       <c r="K12" t="n">
-        <v>1.3098</v>
+        <v>3.639900000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.6336000000000001</v>
+        <v>6.954199999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.3445</v>
+        <v>-14.1321</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.4792</v>
+        <v>-6.1577</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1346</v>
+        <v>-7.9744</v>
       </c>
       <c r="P12" t="n">
-        <v>0.586</v>
+        <v>4.1021</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-41.9983</v>
       </c>
       <c r="R12" t="n">
-        <v>0.586</v>
+        <v>46.101</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2757</v>
+        <v>1.4377</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4842</v>
+        <v>2.0444</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2085</v>
+        <v>-0.607</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.2772</v>
+        <v>-0.8662000000000005</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>19.0561</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.2772</v>
+        <v>-19.9225</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>B. MARTI CAPELLA</t>
+          <t>J. CASCALES FERNANDEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.242</v>
+        <v>0.6324000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1767</v>
+        <v>-2.7688</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.4186</v>
+        <v>3.4013</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.5935</v>
+        <v>-0.06030000000000013</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.5935</v>
+        <v>-1.0449</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>0.9848000000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0205</v>
+        <v>2.5029</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0205</v>
+        <v>-0.9121000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>3.4149</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.614</v>
+        <v>-2.5631</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.614</v>
+        <v>-0.1328999999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>-2.4301</v>
       </c>
       <c r="P13" t="n">
-        <v>0.1953</v>
+        <v>3.1255</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-6.0556</v>
       </c>
       <c r="R13" t="n">
-        <v>0.1953</v>
+        <v>9.181100000000001</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.121</v>
+        <v>2.0766</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.121</v>
+        <v>1.835</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>0.2416</v>
       </c>
       <c r="V13" t="n">
-        <v>0.2772</v>
+        <v>-4.5095</v>
       </c>
       <c r="W13" t="n">
-        <v>0.2772</v>
+        <v>-1.0512</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-3.4584</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>H. LOUASSA</t>
+          <t>N. ARRANZ JARAMILLO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.508899999999999</v>
+        <v>0.3763</v>
       </c>
       <c r="E14" t="n">
-        <v>-6.7635</v>
+        <v>0.3942</v>
       </c>
       <c r="F14" t="n">
-        <v>5.2545</v>
+        <v>-0.0179</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.6325999999999999</v>
+        <v>0.3316</v>
       </c>
       <c r="H14" t="n">
-        <v>2.6436</v>
+        <v>0.8307</v>
       </c>
       <c r="I14" t="n">
-        <v>-3.2765</v>
+        <v>-0.499</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.7459</v>
+        <v>0.6762</v>
       </c>
       <c r="K14" t="n">
-        <v>1.6639</v>
+        <v>1.3098</v>
       </c>
       <c r="L14" t="n">
-        <v>-3.41</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>1.1133</v>
+        <v>-0.3445</v>
       </c>
       <c r="N14" t="n">
-        <v>0.9796</v>
+        <v>-0.4792</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1336000000000001</v>
+        <v>0.1346</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.3674</v>
+        <v>0.586</v>
       </c>
       <c r="Q14" t="n">
-        <v>-4.8835</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>3.5162</v>
+        <v>0.586</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.1694</v>
+        <v>-0.2641</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.0206</v>
+        <v>-0.282</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1488</v>
+        <v>0.0178</v>
       </c>
       <c r="V14" t="n">
-        <v>1.6604</v>
+        <v>-0.2772</v>
       </c>
       <c r="W14" t="n">
-        <v>0.8865</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7739000000000001</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. CASCALES FERNANDEZ</t>
+          <t>B. MARTI CAPELLA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-3.6694</v>
+        <v>-0.242</v>
       </c>
       <c r="E15" t="n">
-        <v>-5.6599</v>
+        <v>0.1767</v>
       </c>
       <c r="F15" t="n">
-        <v>1.9905</v>
+        <v>-0.4186</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.06030000000000013</v>
+        <v>-0.5935</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.0449</v>
+        <v>-0.5935</v>
       </c>
       <c r="I15" t="n">
-        <v>0.9848000000000001</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>2.5029</v>
+        <v>0.0205</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.9121000000000001</v>
+        <v>0.0205</v>
       </c>
       <c r="L15" t="n">
-        <v>3.4149</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.5631</v>
+        <v>-0.614</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1328999999999999</v>
+        <v>-0.614</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.4301</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>3.1255</v>
+        <v>0.1953</v>
       </c>
       <c r="Q15" t="n">
-        <v>-6.0556</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>9.181100000000001</v>
+        <v>0.1953</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.2251</v>
+        <v>-0.121</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.056</v>
+        <v>-0.121</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.1692</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>-4.5095</v>
+        <v>0.2772</v>
       </c>
       <c r="W15" t="n">
-        <v>-1.0512</v>
+        <v>0.2772</v>
       </c>
       <c r="X15" t="n">
-        <v>-3.4584</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. PLANELL IGLESIAS</t>
+          <t>H. LOUASSA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,70 +1654,70 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>-6.7375</v>
+        <v>-0.7635000000000005</v>
       </c>
       <c r="E16" t="n">
-        <v>-8.350099999999999</v>
+        <v>-6.5613</v>
       </c>
       <c r="F16" t="n">
-        <v>1.6126</v>
+        <v>5.797800000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.9663</v>
+        <v>-0.6325999999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.2111</v>
+        <v>2.6436</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.7553000000000001</v>
+        <v>-3.2765</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1201</v>
+        <v>-1.7459</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.7444999999999998</v>
+        <v>1.6639</v>
       </c>
       <c r="L16" t="n">
-        <v>0.8645</v>
+        <v>-3.41</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.0865</v>
+        <v>1.1133</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.4665</v>
+        <v>0.9796</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.6198</v>
+        <v>0.1336000000000001</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.5395</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q16" t="n">
-        <v>-7.8136</v>
+        <v>-4.8835</v>
       </c>
       <c r="R16" t="n">
-        <v>5.2742</v>
+        <v>3.5162</v>
       </c>
       <c r="S16" t="n">
-        <v>2.7783</v>
+        <v>-0.4237</v>
       </c>
       <c r="T16" t="n">
-        <v>0.7267</v>
+        <v>-0.8184</v>
       </c>
       <c r="U16" t="n">
-        <v>2.0514</v>
+        <v>0.3946</v>
       </c>
       <c r="V16" t="n">
-        <v>-4.0099</v>
+        <v>1.6604</v>
       </c>
       <c r="W16" t="n">
-        <v>-1.3832</v>
+        <v>0.8865</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.6267</v>
+        <v>0.7739000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>8</v>
       </c>
       <c r="D17" t="n">
-        <v>-7.4738</v>
+        <v>-6.0261</v>
       </c>
       <c r="E17" t="n">
-        <v>-5.4432</v>
+        <v>-3.9672</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.0305</v>
+        <v>-2.0591</v>
       </c>
       <c r="G17" t="n">
         <v>-9.0303</v>
@@ -1780,13 +1780,13 @@
         <v>4.8835</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.6854</v>
+        <v>-0.2379</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.788</v>
+        <v>-0.312</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1026</v>
+        <v>0.07419999999999999</v>
       </c>
       <c r="V17" t="n">
         <v>-0.6648000000000001</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. SALO BLAYA</t>
+          <t>A. PLANELL IGLESIAS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,76 +1810,76 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>-11.8935</v>
+        <v>-8.4049</v>
       </c>
       <c r="E18" t="n">
-        <v>-5.2342</v>
+        <v>-9.2807</v>
       </c>
       <c r="F18" t="n">
-        <v>-6.6594</v>
+        <v>0.8758999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>-12.5309</v>
+        <v>-2.9663</v>
       </c>
       <c r="H18" t="n">
-        <v>-10.5284</v>
+        <v>-2.2111</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.0025</v>
+        <v>-0.7553000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.0419</v>
+        <v>0.1201</v>
       </c>
       <c r="K18" t="n">
-        <v>-7.0596</v>
+        <v>-0.7444999999999998</v>
       </c>
       <c r="L18" t="n">
-        <v>5.0179</v>
+        <v>0.8645</v>
       </c>
       <c r="M18" t="n">
-        <v>-10.4888</v>
+        <v>-3.0865</v>
       </c>
       <c r="N18" t="n">
-        <v>-3.4684</v>
+        <v>-1.4665</v>
       </c>
       <c r="O18" t="n">
-        <v>-7.0201</v>
+        <v>-1.6198</v>
       </c>
       <c r="P18" t="n">
-        <v>4.2976</v>
+        <v>-2.5395</v>
       </c>
       <c r="Q18" t="n">
-        <v>-16.6039</v>
+        <v>-7.8136</v>
       </c>
       <c r="R18" t="n">
-        <v>20.9016</v>
+        <v>5.2742</v>
       </c>
       <c r="S18" t="n">
-        <v>6.9466</v>
+        <v>1.1108</v>
       </c>
       <c r="T18" t="n">
-        <v>9.9756</v>
+        <v>-0.204</v>
       </c>
       <c r="U18" t="n">
-        <v>-3.0285</v>
+        <v>1.3148</v>
       </c>
       <c r="V18" t="n">
-        <v>-10.6066</v>
+        <v>-4.0099</v>
       </c>
       <c r="W18" t="n">
-        <v>3.436199999999999</v>
+        <v>-1.3832</v>
       </c>
       <c r="X18" t="n">
-        <v>-14.0431</v>
+        <v>-2.6267</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>I. JUNCADELLA ENFEDAQUE</t>
+          <t>A. SALO BLAYA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,70 +1888,70 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D19" t="n">
-        <v>-20.2846</v>
+        <v>-15.6875</v>
       </c>
       <c r="E19" t="n">
-        <v>-25.4285</v>
+        <v>-10.9579</v>
       </c>
       <c r="F19" t="n">
-        <v>5.143800000000001</v>
+        <v>-4.7297</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.5382</v>
+        <v>-12.5309</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.517799999999999</v>
+        <v>-10.5284</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.0204</v>
+        <v>-2.0025</v>
       </c>
       <c r="J19" t="n">
-        <v>10.5942</v>
+        <v>-2.0419</v>
       </c>
       <c r="K19" t="n">
-        <v>3.639900000000001</v>
+        <v>-7.0596</v>
       </c>
       <c r="L19" t="n">
-        <v>6.954199999999999</v>
+        <v>5.0179</v>
       </c>
       <c r="M19" t="n">
-        <v>-14.1321</v>
+        <v>-10.4888</v>
       </c>
       <c r="N19" t="n">
-        <v>-6.1577</v>
+        <v>-3.4684</v>
       </c>
       <c r="O19" t="n">
-        <v>-7.9744</v>
+        <v>-7.0201</v>
       </c>
       <c r="P19" t="n">
-        <v>4.1021</v>
+        <v>4.2976</v>
       </c>
       <c r="Q19" t="n">
-        <v>-41.9983</v>
+        <v>-16.6039</v>
       </c>
       <c r="R19" t="n">
-        <v>46.101</v>
+        <v>20.9016</v>
       </c>
       <c r="S19" t="n">
-        <v>-19.9821</v>
+        <v>3.1526</v>
       </c>
       <c r="T19" t="n">
-        <v>-13.0803</v>
+        <v>4.252</v>
       </c>
       <c r="U19" t="n">
-        <v>-6.902500000000001</v>
+        <v>-1.0991</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.8662000000000005</v>
+        <v>-10.6066</v>
       </c>
       <c r="W19" t="n">
-        <v>19.0561</v>
+        <v>3.436199999999999</v>
       </c>
       <c r="X19" t="n">
-        <v>-19.9225</v>
+        <v>-14.0431</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>26</v>
       </c>
       <c r="D20" t="n">
-        <v>189.168</v>
+        <v>215.6765</v>
       </c>
       <c r="E20" t="n">
-        <v>97.3492</v>
+        <v>104.3099</v>
       </c>
       <c r="F20" t="n">
-        <v>91.8192</v>
+        <v>111.3673</v>
       </c>
       <c r="G20" t="n">
         <v>129.7084</v>
@@ -1984,7 +1984,7 @@
         <v>124.3621</v>
       </c>
       <c r="I20" t="n">
-        <v>5.347199999999997</v>
+        <v>5.347199999999998</v>
       </c>
       <c r="J20" t="n">
         <v>298.9616</v>
@@ -1999,10 +1999,10 @@
         <v>-169.2523</v>
       </c>
       <c r="N20" t="n">
-        <v>-74.0014</v>
+        <v>-74.00139999999999</v>
       </c>
       <c r="O20" t="n">
-        <v>-95.25160000000001</v>
+        <v>-95.2516</v>
       </c>
       <c r="P20" t="n">
         <v>28.3243</v>
@@ -2014,13 +2014,13 @@
         <v>414.1265</v>
       </c>
       <c r="S20" t="n">
-        <v>51.42189999999999</v>
+        <v>77.93090000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>46.6534</v>
+        <v>53.6134</v>
       </c>
       <c r="U20" t="n">
-        <v>4.768199999999996</v>
+        <v>24.31769999999999</v>
       </c>
       <c r="V20" t="n">
         <v>-20.28659999999999</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_CB NAVÀS VISCOLA.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_CB NAVÀS VISCOLA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X20"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -874,70 +874,70 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D6" t="n">
-        <v>29.3441</v>
+        <v>24.4055</v>
       </c>
       <c r="E6" t="n">
-        <v>29.8979</v>
+        <v>24.4055</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5536999999999999</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>12.6995</v>
+        <v>24.4055</v>
       </c>
       <c r="H6" t="n">
-        <v>3.7569</v>
+        <v>11.0518</v>
       </c>
       <c r="I6" t="n">
-        <v>8.942899999999998</v>
+        <v>13.354</v>
       </c>
       <c r="J6" t="n">
-        <v>45.6274</v>
+        <v>24.4055</v>
       </c>
       <c r="K6" t="n">
-        <v>19.6691</v>
+        <v>11.0518</v>
       </c>
       <c r="L6" t="n">
-        <v>25.9584</v>
+        <v>13.354</v>
       </c>
       <c r="M6" t="n">
-        <v>-32.928</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-15.9124</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>-17.0158</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>8.7903</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-42.5845</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>51.3752</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>5.9516</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.8079</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2.1438</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.903</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>23.0469</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-21.1442</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B. RODRÍGUEZ CHAVARRIA</t>
+          <t>P. MONES RIERA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="D10" t="n">
-        <v>2.9517</v>
+        <v>4.938899999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>2.5159</v>
+        <v>5.493000000000002</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4358</v>
+        <v>-0.5536999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>3.0012</v>
+        <v>-11.7058</v>
       </c>
       <c r="H10" t="n">
-        <v>1.2205</v>
+        <v>-7.294599999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>1.7807</v>
+        <v>-4.4108</v>
       </c>
       <c r="J10" t="n">
-        <v>1.6727</v>
+        <v>21.2222</v>
       </c>
       <c r="K10" t="n">
-        <v>0.4309999999999999</v>
+        <v>8.617799999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>1.2416</v>
+        <v>12.6046</v>
       </c>
       <c r="M10" t="n">
-        <v>1.3286</v>
+        <v>-32.928</v>
       </c>
       <c r="N10" t="n">
-        <v>0.7895</v>
+        <v>-15.9124</v>
       </c>
       <c r="O10" t="n">
-        <v>0.5391</v>
+        <v>-17.0158</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>8.7903</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9767</v>
+        <v>-42.5845</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9766999999999999</v>
+        <v>51.3752</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0495</v>
+        <v>5.9516</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6012999999999999</v>
+        <v>3.8079</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6508</v>
+        <v>2.1438</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.903</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2186</v>
+        <v>23.0469</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2186</v>
+        <v>-21.1442</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>L. FONT TÀPIA</t>
+          <t>B. RODRIGUEZ CHAVARRIA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>1.6745</v>
+        <v>2.9517</v>
       </c>
       <c r="E11" t="n">
-        <v>1.2749</v>
+        <v>2.5159</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3996</v>
+        <v>0.4358</v>
       </c>
       <c r="G11" t="n">
-        <v>1.6794</v>
+        <v>3.0012</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4249</v>
+        <v>1.2205</v>
       </c>
       <c r="I11" t="n">
-        <v>1.2544</v>
+        <v>1.7807</v>
       </c>
       <c r="J11" t="n">
-        <v>1.2749</v>
+        <v>1.6727</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0205</v>
+        <v>0.4309999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>1.2544</v>
+        <v>1.2416</v>
       </c>
       <c r="M11" t="n">
-        <v>0.4045</v>
+        <v>1.3286</v>
       </c>
       <c r="N11" t="n">
-        <v>0.4045</v>
+        <v>0.7895</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>0.5391</v>
       </c>
       <c r="P11" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R11" t="n">
-        <v>0.1953</v>
+        <v>0.9766999999999999</v>
       </c>
       <c r="S11" t="n">
-        <v>0.077</v>
+        <v>-0.0495</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>0.6012999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>0.077</v>
+        <v>-0.6508</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.2772</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>I. JUNCADELLA ENFEDAQUE</t>
+          <t>L. FONT TAPIA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1.1352</v>
+        <v>1.6745</v>
       </c>
       <c r="E12" t="n">
-        <v>-10.304</v>
+        <v>1.2749</v>
       </c>
       <c r="F12" t="n">
-        <v>11.4393</v>
+        <v>0.3996</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.5382</v>
+        <v>1.6794</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.517799999999999</v>
+        <v>0.4249</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.0204</v>
+        <v>1.2544</v>
       </c>
       <c r="J12" t="n">
-        <v>10.5942</v>
+        <v>1.2749</v>
       </c>
       <c r="K12" t="n">
-        <v>3.639900000000001</v>
+        <v>0.0205</v>
       </c>
       <c r="L12" t="n">
-        <v>6.954199999999999</v>
+        <v>1.2544</v>
       </c>
       <c r="M12" t="n">
-        <v>-14.1321</v>
+        <v>0.4045</v>
       </c>
       <c r="N12" t="n">
-        <v>-6.1577</v>
+        <v>0.4045</v>
       </c>
       <c r="O12" t="n">
-        <v>-7.9744</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>4.1021</v>
+        <v>0.1953</v>
       </c>
       <c r="Q12" t="n">
-        <v>-41.9983</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>46.101</v>
+        <v>0.1953</v>
       </c>
       <c r="S12" t="n">
-        <v>1.4377</v>
+        <v>0.077</v>
       </c>
       <c r="T12" t="n">
-        <v>2.0444</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.607</v>
+        <v>0.077</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.8662000000000005</v>
+        <v>-0.2772</v>
       </c>
       <c r="W12" t="n">
-        <v>19.0561</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-19.9225</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. CASCALES FERNANDEZ</t>
+          <t>I. JUNCADELLA ENFEDAQUE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6324000000000001</v>
+        <v>1.1352</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.7688</v>
+        <v>-10.304</v>
       </c>
       <c r="F13" t="n">
-        <v>3.4013</v>
+        <v>11.4393</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.06030000000000013</v>
+        <v>-3.5382</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.0449</v>
+        <v>-2.517799999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>0.9848000000000001</v>
+        <v>-1.0204</v>
       </c>
       <c r="J13" t="n">
-        <v>2.5029</v>
+        <v>10.5942</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.9121000000000001</v>
+        <v>3.639900000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>3.4149</v>
+        <v>6.954199999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.5631</v>
+        <v>-14.1321</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.1328999999999999</v>
+        <v>-6.1577</v>
       </c>
       <c r="O13" t="n">
-        <v>-2.4301</v>
+        <v>-7.9744</v>
       </c>
       <c r="P13" t="n">
-        <v>3.1255</v>
+        <v>4.1021</v>
       </c>
       <c r="Q13" t="n">
-        <v>-6.0556</v>
+        <v>-41.9983</v>
       </c>
       <c r="R13" t="n">
-        <v>9.181100000000001</v>
+        <v>46.101</v>
       </c>
       <c r="S13" t="n">
-        <v>2.0766</v>
+        <v>1.4377</v>
       </c>
       <c r="T13" t="n">
-        <v>1.835</v>
+        <v>2.0444</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2416</v>
+        <v>-0.607</v>
       </c>
       <c r="V13" t="n">
-        <v>-4.5095</v>
+        <v>-0.8662000000000005</v>
       </c>
       <c r="W13" t="n">
-        <v>-1.0512</v>
+        <v>19.0561</v>
       </c>
       <c r="X13" t="n">
-        <v>-3.4584</v>
+        <v>-19.9225</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>N. ARRANZ JARAMILLO</t>
+          <t>J. CASCALES FERNANDEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3763</v>
+        <v>0.6324000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3942</v>
+        <v>-2.7688</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.0179</v>
+        <v>3.4013</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3316</v>
+        <v>-0.06030000000000013</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8307</v>
+        <v>-1.0449</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.499</v>
+        <v>0.9848000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6762</v>
+        <v>2.5029</v>
       </c>
       <c r="K14" t="n">
-        <v>1.3098</v>
+        <v>-0.9121000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.6336000000000001</v>
+        <v>3.4149</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.3445</v>
+        <v>-2.5631</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.4792</v>
+        <v>-0.1328999999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1346</v>
+        <v>-2.4301</v>
       </c>
       <c r="P14" t="n">
-        <v>0.586</v>
+        <v>3.1255</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-6.0556</v>
       </c>
       <c r="R14" t="n">
-        <v>0.586</v>
+        <v>9.181100000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2641</v>
+        <v>2.0766</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.282</v>
+        <v>1.835</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0178</v>
+        <v>0.2416</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.2772</v>
+        <v>-4.5095</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>-1.0512</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.2772</v>
+        <v>-3.4584</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B. MARTI CAPELLA</t>
+          <t>N. ARRANZ JARAMILLO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.242</v>
+        <v>0.3763</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1767</v>
+        <v>0.3942</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4186</v>
+        <v>-0.0179</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.5935</v>
+        <v>0.3316</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.5935</v>
+        <v>0.8307</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>-0.499</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0205</v>
+        <v>0.6762</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0205</v>
+        <v>1.3098</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.614</v>
+        <v>-0.3445</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.614</v>
+        <v>-0.4792</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>0.1346</v>
       </c>
       <c r="P15" t="n">
-        <v>0.1953</v>
+        <v>0.586</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.1953</v>
+        <v>0.586</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.121</v>
+        <v>-0.2641</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.121</v>
+        <v>-0.282</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>0.0178</v>
       </c>
       <c r="V15" t="n">
-        <v>0.2772</v>
+        <v>-0.2772</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>H. LOUASSA</t>
+          <t>B. MARTI CAPELLA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.7635000000000005</v>
+        <v>-0.242</v>
       </c>
       <c r="E16" t="n">
-        <v>-6.5613</v>
+        <v>0.1767</v>
       </c>
       <c r="F16" t="n">
-        <v>5.797800000000001</v>
+        <v>-0.4186</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.6325999999999999</v>
+        <v>-0.5935</v>
       </c>
       <c r="H16" t="n">
-        <v>2.6436</v>
+        <v>-0.5935</v>
       </c>
       <c r="I16" t="n">
-        <v>-3.2765</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.7459</v>
+        <v>0.0205</v>
       </c>
       <c r="K16" t="n">
-        <v>1.6639</v>
+        <v>0.0205</v>
       </c>
       <c r="L16" t="n">
-        <v>-3.41</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.1133</v>
+        <v>-0.614</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9796</v>
+        <v>-0.614</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1336000000000001</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.3674</v>
+        <v>0.1953</v>
       </c>
       <c r="Q16" t="n">
-        <v>-4.8835</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>3.5162</v>
+        <v>0.1953</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4237</v>
+        <v>-0.121</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8184</v>
+        <v>-0.121</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3946</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.6604</v>
+        <v>0.2772</v>
       </c>
       <c r="W16" t="n">
-        <v>0.8865</v>
+        <v>0.2772</v>
       </c>
       <c r="X16" t="n">
-        <v>0.7739000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. COSTA RABANEDA</t>
+          <t>H. LOUASSA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,76 +1732,76 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>-6.0261</v>
+        <v>-0.7635000000000005</v>
       </c>
       <c r="E17" t="n">
-        <v>-3.9672</v>
+        <v>-6.5613</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.0591</v>
+        <v>5.797800000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>-9.0303</v>
+        <v>-0.6325999999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.8952</v>
+        <v>2.6436</v>
       </c>
       <c r="I17" t="n">
-        <v>-6.1351</v>
+        <v>-3.2765</v>
       </c>
       <c r="J17" t="n">
-        <v>-5.670100000000001</v>
+        <v>-1.7459</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.3452999999999999</v>
+        <v>1.6639</v>
       </c>
       <c r="L17" t="n">
-        <v>-5.3246</v>
+        <v>-3.41</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.3603</v>
+        <v>1.1133</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.55</v>
+        <v>0.9796</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.8103999999999999</v>
+        <v>0.1336000000000001</v>
       </c>
       <c r="P17" t="n">
-        <v>3.9068</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9767</v>
+        <v>-4.8835</v>
       </c>
       <c r="R17" t="n">
-        <v>4.8835</v>
+        <v>3.5162</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2379</v>
+        <v>-0.4237</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.312</v>
+        <v>-0.8184</v>
       </c>
       <c r="U17" t="n">
-        <v>0.07419999999999999</v>
+        <v>0.3946</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.6648000000000001</v>
+        <v>1.6604</v>
       </c>
       <c r="W17" t="n">
-        <v>2.9916</v>
+        <v>0.8865</v>
       </c>
       <c r="X17" t="n">
-        <v>-3.6565</v>
+        <v>0.7739000000000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. PLANELL IGLESIAS</t>
+          <t>M. COSTA RABANEDA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,76 +1810,76 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D18" t="n">
-        <v>-8.4049</v>
+        <v>-6.0261</v>
       </c>
       <c r="E18" t="n">
-        <v>-9.2807</v>
+        <v>-3.9672</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8758999999999999</v>
+        <v>-2.0591</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.9663</v>
+        <v>-9.0303</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.2111</v>
+        <v>-2.8952</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.7553000000000001</v>
+        <v>-6.1351</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1201</v>
+        <v>-5.670100000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.7444999999999998</v>
+        <v>-0.3452999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>0.8645</v>
+        <v>-5.3246</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.0865</v>
+        <v>-3.3603</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.4665</v>
+        <v>-2.55</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.6198</v>
+        <v>-0.8103999999999999</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.5395</v>
+        <v>3.9068</v>
       </c>
       <c r="Q18" t="n">
-        <v>-7.8136</v>
+        <v>-0.9767</v>
       </c>
       <c r="R18" t="n">
-        <v>5.2742</v>
+        <v>4.8835</v>
       </c>
       <c r="S18" t="n">
-        <v>1.1108</v>
+        <v>-0.2379</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.204</v>
+        <v>-0.312</v>
       </c>
       <c r="U18" t="n">
-        <v>1.3148</v>
+        <v>0.07419999999999999</v>
       </c>
       <c r="V18" t="n">
-        <v>-4.0099</v>
+        <v>-0.6648000000000001</v>
       </c>
       <c r="W18" t="n">
-        <v>-1.3832</v>
+        <v>2.9916</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.6267</v>
+        <v>-3.6565</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. SALO BLAYA</t>
+          <t>A. PLANELL IGLESIAS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,147 +1888,225 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>-15.6875</v>
+        <v>-8.4049</v>
       </c>
       <c r="E19" t="n">
-        <v>-10.9579</v>
+        <v>-9.2807</v>
       </c>
       <c r="F19" t="n">
-        <v>-4.7297</v>
+        <v>0.8758999999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>-12.5309</v>
+        <v>-2.9663</v>
       </c>
       <c r="H19" t="n">
-        <v>-10.5284</v>
+        <v>-2.2111</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.0025</v>
+        <v>-0.7553000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.0419</v>
+        <v>0.1201</v>
       </c>
       <c r="K19" t="n">
-        <v>-7.0596</v>
+        <v>-0.7444999999999998</v>
       </c>
       <c r="L19" t="n">
-        <v>5.0179</v>
+        <v>0.8645</v>
       </c>
       <c r="M19" t="n">
-        <v>-10.4888</v>
+        <v>-3.0865</v>
       </c>
       <c r="N19" t="n">
-        <v>-3.4684</v>
+        <v>-1.4665</v>
       </c>
       <c r="O19" t="n">
-        <v>-7.0201</v>
+        <v>-1.6198</v>
       </c>
       <c r="P19" t="n">
-        <v>4.2976</v>
+        <v>-2.5395</v>
       </c>
       <c r="Q19" t="n">
-        <v>-16.6039</v>
+        <v>-7.8136</v>
       </c>
       <c r="R19" t="n">
-        <v>20.9016</v>
+        <v>5.2742</v>
       </c>
       <c r="S19" t="n">
-        <v>3.1526</v>
+        <v>1.1108</v>
       </c>
       <c r="T19" t="n">
-        <v>4.252</v>
+        <v>-0.204</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.0991</v>
+        <v>1.3148</v>
       </c>
       <c r="V19" t="n">
-        <v>-10.6066</v>
+        <v>-4.0099</v>
       </c>
       <c r="W19" t="n">
-        <v>3.436199999999999</v>
+        <v>-1.3832</v>
       </c>
       <c r="X19" t="n">
-        <v>-14.0431</v>
+        <v>-2.6267</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>A. SALO BLAYA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>CB NAVÀS VISCOLA</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>24</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-15.6875</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-10.9579</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-4.7297</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-12.5309</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-10.5284</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-2.0025</v>
+      </c>
+      <c r="J20" t="n">
+        <v>-2.0419</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-7.0596</v>
+      </c>
+      <c r="L20" t="n">
+        <v>5.0179</v>
+      </c>
+      <c r="M20" t="n">
+        <v>-10.4888</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-3.4684</v>
+      </c>
+      <c r="O20" t="n">
+        <v>-7.0201</v>
+      </c>
+      <c r="P20" t="n">
+        <v>4.2976</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>-16.6039</v>
+      </c>
+      <c r="R20" t="n">
+        <v>20.9016</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.1526</v>
+      </c>
+      <c r="T20" t="n">
+        <v>4.252</v>
+      </c>
+      <c r="U20" t="n">
+        <v>-1.0991</v>
+      </c>
+      <c r="V20" t="n">
+        <v>-10.6066</v>
+      </c>
+      <c r="W20" t="n">
+        <v>3.436199999999999</v>
+      </c>
+      <c r="X20" t="n">
+        <v>-14.0431</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>--- TOTAL ---</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>CB NAVÀS VISCOLA</t>
         </is>
       </c>
-      <c r="C20" t="n">
+      <c r="C21" t="n">
         <v>26</v>
       </c>
-      <c r="D20" t="n">
-        <v>215.6765</v>
-      </c>
-      <c r="E20" t="n">
-        <v>104.3099</v>
-      </c>
-      <c r="F20" t="n">
+      <c r="D21" t="n">
+        <v>215.6768</v>
+      </c>
+      <c r="E21" t="n">
+        <v>104.3105</v>
+      </c>
+      <c r="F21" t="n">
         <v>111.3673</v>
       </c>
-      <c r="G20" t="n">
-        <v>129.7084</v>
-      </c>
-      <c r="H20" t="n">
-        <v>124.3621</v>
-      </c>
-      <c r="I20" t="n">
-        <v>5.347199999999998</v>
-      </c>
-      <c r="J20" t="n">
-        <v>298.9616</v>
-      </c>
-      <c r="K20" t="n">
-        <v>198.3631</v>
-      </c>
-      <c r="L20" t="n">
-        <v>100.5995</v>
-      </c>
-      <c r="M20" t="n">
+      <c r="G21" t="n">
+        <v>129.7086</v>
+      </c>
+      <c r="H21" t="n">
+        <v>124.3624</v>
+      </c>
+      <c r="I21" t="n">
+        <v>5.347500000000001</v>
+      </c>
+      <c r="J21" t="n">
+        <v>298.9619</v>
+      </c>
+      <c r="K21" t="n">
+        <v>198.3636</v>
+      </c>
+      <c r="L21" t="n">
+        <v>100.5997</v>
+      </c>
+      <c r="M21" t="n">
         <v>-169.2523</v>
       </c>
-      <c r="N20" t="n">
-        <v>-74.00139999999999</v>
-      </c>
-      <c r="O20" t="n">
+      <c r="N21" t="n">
+        <v>-74.0014</v>
+      </c>
+      <c r="O21" t="n">
         <v>-95.2516</v>
       </c>
-      <c r="P20" t="n">
+      <c r="P21" t="n">
         <v>28.3243</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="Q21" t="n">
         <v>-385.8001</v>
       </c>
-      <c r="R20" t="n">
+      <c r="R21" t="n">
         <v>414.1265</v>
       </c>
-      <c r="S20" t="n">
+      <c r="S21" t="n">
         <v>77.93090000000001</v>
       </c>
-      <c r="T20" t="n">
-        <v>53.6134</v>
-      </c>
-      <c r="U20" t="n">
-        <v>24.31769999999999</v>
-      </c>
-      <c r="V20" t="n">
+      <c r="T21" t="n">
+        <v>53.61340000000001</v>
+      </c>
+      <c r="U21" t="n">
+        <v>24.3177</v>
+      </c>
+      <c r="V21" t="n">
         <v>-20.28659999999999</v>
       </c>
-      <c r="W20" t="n">
+      <c r="W21" t="n">
         <v>137.5344</v>
       </c>
-      <c r="X20" t="n">
+      <c r="X21" t="n">
         <v>-157.8221</v>
       </c>
     </row>
